--- a/sharedata/excel/Z-装备属性表(EquipAttrData).xlsx
+++ b/sharedata/excel/Z-装备属性表(EquipAttrData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>装备属性表</t>
   </si>
@@ -89,6 +89,102 @@
   </si>
   <si>
     <t>uniq</t>
+  </si>
+  <si>
+    <t>攻击固定</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_攻击固定</t>
+  </si>
+  <si>
+    <t>atk</t>
+  </si>
+  <si>
+    <t>flat</t>
+  </si>
+  <si>
+    <t>攻击比例</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_攻击比例</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>防御固定</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_防御固定</t>
+  </si>
+  <si>
+    <t>def</t>
+  </si>
+  <si>
+    <t>防御比例</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_防御比例</t>
+  </si>
+  <si>
+    <t>智力固定</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_智力固定</t>
+  </si>
+  <si>
+    <t>intelligence</t>
+  </si>
+  <si>
+    <t>智力比例</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_智力比例</t>
+  </si>
+  <si>
+    <t>统帅固定</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_统帅固定</t>
+  </si>
+  <si>
+    <t>command</t>
+  </si>
+  <si>
+    <t>统帅比例</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_统帅比例</t>
+  </si>
+  <si>
+    <t>PVE移动力固定</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_PVE移动力固定</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>PVE移动力比例</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_PVE移动力比例</t>
+  </si>
+  <si>
+    <t>先攻固定</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_先攻固定</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>先攻比例</t>
+  </si>
+  <si>
+    <t>$Lang$装备属性_先攻比例</t>
   </si>
 </sst>
 </file>
@@ -121,6 +217,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -270,13 +373,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -605,157 +701,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -768,11 +862,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1246,23 +1337,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.1166666666667" customWidth="1"/>
-    <col min="2" max="2" width="9.38333333333333" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="9.91666666666667" customWidth="1"/>
-    <col min="6" max="6" width="11.0416666666667" customWidth="1"/>
+    <col min="1" max="1" width="14.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" ht="16.5" spans="1:6">
       <c r="A2" s="2"/>
@@ -1272,7 +1364,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:6">
+    <row r="3" ht="15" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1292,7 +1384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:6">
+    <row r="4" ht="16.5" spans="1:6">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1312,7 +1404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:6">
+    <row r="5" ht="16.5" spans="1:6">
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
@@ -1332,7 +1424,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:6">
+    <row r="6" ht="16.5" spans="1:6">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -1346,209 +1438,209 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:6">
+    <row r="7" ht="16.5" spans="1:6">
       <c r="A7" s="5"/>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="str">
-        <v>攻击固定</v>
-      </c>
-      <c r="D7" s="6" t="str">
-        <v>$Lang$装备属性_攻击固定</v>
-      </c>
-      <c r="E7" s="6" t="str">
-        <v>atk</v>
-      </c>
-      <c r="F7" s="6" t="str">
-        <v>flat</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="B8" t="n" s="6">
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:6">
+      <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" t="str" s="6">
-        <v>攻击比例</v>
-      </c>
-      <c r="D8" t="str" s="6">
-        <v>$Lang$装备属性_攻击比例</v>
-      </c>
-      <c r="E8" t="str" s="6">
-        <v>atk</v>
-      </c>
-      <c r="F8" t="str" s="6">
-        <v>rate</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="B9" t="n" s="6">
+      <c r="C8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:6">
+      <c r="B9" s="6">
         <v>3</v>
       </c>
-      <c r="C9" t="str" s="6">
-        <v>防御固定</v>
-      </c>
-      <c r="D9" t="str" s="6">
-        <v>$Lang$装备属性_防御固定</v>
-      </c>
-      <c r="E9" t="str" s="6">
-        <v>def</v>
-      </c>
-      <c r="F9" t="str" s="6">
-        <v>flat</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="B10" t="n" s="6">
+      <c r="C9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:6">
+      <c r="B10" s="6">
         <v>4</v>
       </c>
-      <c r="C10" t="str" s="6">
-        <v>防御比例</v>
-      </c>
-      <c r="D10" t="str" s="6">
-        <v>$Lang$装备属性_防御比例</v>
-      </c>
-      <c r="E10" t="str" s="6">
-        <v>def</v>
-      </c>
-      <c r="F10" t="str" s="6">
-        <v>rate</v>
-      </c>
-    </row>
-    <row r="11" ht="33.0" customHeight="1">
-      <c r="B11" t="n" s="6">
+      <c r="C10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:6">
+      <c r="B11" s="6">
         <v>5</v>
       </c>
-      <c r="C11" t="str" s="6">
-        <v>智力固定</v>
-      </c>
-      <c r="D11" t="str" s="6">
-        <v>$Lang$装备属性_智力固定</v>
-      </c>
-      <c r="E11" t="str" s="7">
-        <v>intelligence</v>
-      </c>
-      <c r="F11" t="str" s="6">
-        <v>flat</v>
-      </c>
-    </row>
-    <row r="12" ht="33.0" customHeight="1">
-      <c r="B12" t="n" s="6">
+      <c r="C11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:6">
+      <c r="B12" s="6">
         <v>6</v>
       </c>
-      <c r="C12" t="str" s="6">
-        <v>智力比例</v>
-      </c>
-      <c r="D12" t="str" s="6">
-        <v>$Lang$装备属性_智力比例</v>
-      </c>
-      <c r="E12" t="str" s="7">
-        <v>intelligence</v>
-      </c>
-      <c r="F12" t="str" s="6">
-        <v>rate</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="B13" t="n" s="6">
+      <c r="C12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:6">
+      <c r="B13" s="6">
         <v>7</v>
       </c>
-      <c r="C13" t="str" s="6">
-        <v>统帅固定</v>
-      </c>
-      <c r="D13" t="str" s="6">
-        <v>$Lang$装备属性_统帅固定</v>
-      </c>
-      <c r="E13" t="str" s="6">
-        <v>command</v>
-      </c>
-      <c r="F13" t="str" s="6">
-        <v>flat</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="B14" t="n" s="6">
+      <c r="C13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:6">
+      <c r="B14" s="6">
         <v>8</v>
       </c>
-      <c r="C14" t="str" s="6">
-        <v>统帅比例</v>
-      </c>
-      <c r="D14" t="str" s="6">
-        <v>$Lang$装备属性_统帅比例</v>
-      </c>
-      <c r="E14" t="str" s="6">
-        <v>command</v>
-      </c>
-      <c r="F14" t="str" s="6">
-        <v>rate</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="B15" t="n" s="6">
+      <c r="C14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:6">
+      <c r="B15" s="6">
         <v>9</v>
       </c>
-      <c r="C15" t="str" s="6">
-        <v>PVE移动力固定</v>
-      </c>
-      <c r="D15" t="str" s="6">
-        <v>$Lang$装备属性_PVE移动力固定</v>
-      </c>
-      <c r="E15" t="str" s="6">
-        <v>move</v>
-      </c>
-      <c r="F15" t="str" s="6">
-        <v>flat</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="B16" t="n" s="6">
+      <c r="C15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:6">
+      <c r="B16" s="6">
         <v>10</v>
       </c>
-      <c r="C16" t="str" s="6">
-        <v>PVE移动力比例</v>
-      </c>
-      <c r="D16" t="str" s="6">
-        <v>$Lang$装备属性_PVE移动力比例</v>
-      </c>
-      <c r="E16" t="str" s="6">
-        <v>move</v>
-      </c>
-      <c r="F16" t="str" s="6">
-        <v>rate</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="B17" t="n" s="6">
+      <c r="C16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="2:6">
+      <c r="B17" s="6">
         <v>11</v>
       </c>
-      <c r="C17" t="str" s="6">
-        <v>先攻固定</v>
-      </c>
-      <c r="D17" t="str" s="6">
-        <v>$Lang$装备属性_先攻固定</v>
-      </c>
-      <c r="E17" t="str" s="6">
-        <v>speed</v>
-      </c>
-      <c r="F17" t="str" s="6">
-        <v>flat</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="B18" t="n" s="6">
+      <c r="C17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:6">
+      <c r="B18" s="6">
         <v>12</v>
       </c>
-      <c r="C18" t="str" s="6">
-        <v>先攻比例</v>
-      </c>
-      <c r="D18" t="str" s="6">
-        <v>$Lang$装备属性_先攻比例</v>
-      </c>
-      <c r="E18" t="str" s="6">
-        <v>speed</v>
-      </c>
-      <c r="F18" t="str" s="6">
-        <v>rate</v>
+      <c r="C18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
